--- a/eoe/Assets/Excels/SkillConfig.xlsx
+++ b/eoe/Assets/Excels/SkillConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="38">
   <si>
     <t xml:space="preserve">skillId</t>
   </si>
@@ -43,13 +43,7 @@
     <t xml:space="preserve">projectileSpeed</t>
   </si>
   <si>
-    <t xml:space="preserve">projectileStartDuration</t>
-  </si>
-  <si>
     <t xml:space="preserve">projectileDuration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">projectileEndDuration</t>
   </si>
   <si>
     <t xml:space="preserve">sizeMultiplier</t>
@@ -416,27 +410,26 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr defaultColWidth="15.6328125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="15.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.36"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="4" style="1" width="15.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="20"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="16.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="15.45"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="15.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="1" width="20.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="21.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="20.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="22.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="21" style="1" width="20.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="20.63"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="28" style="1" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="17.54"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15.45"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="20.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="21.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="20.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="22.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="19" style="1" width="20.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="20.63"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16381" min="26" style="1" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16383" min="16382" style="0" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
@@ -510,37 +503,31 @@
       <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>2001</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>8</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>1</v>
@@ -549,45 +536,39 @@
         <v>0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T2" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="U2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="V2" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -596,19 +577,19 @@
         <v>2002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>7</v>
@@ -617,51 +598,45 @@
         <v>0</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>15</v>
+        <v>0.7</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="T3" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="V3" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -670,19 +645,19 @@
         <v>2003</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>10</v>
@@ -691,22 +666,22 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J4" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.8</v>
+        <v>0.15</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>0</v>
@@ -715,7 +690,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="1" t="n">
         <v>0</v>
@@ -723,19 +698,13 @@
       <c r="S4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T4" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="U4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="V4" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="W4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -744,19 +713,19 @@
         <v>2004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>15</v>
@@ -765,22 +734,22 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" s="1" t="n">
         <v>0</v>
@@ -789,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="1" t="n">
         <v>0</v>
@@ -797,19 +766,13 @@
       <c r="S5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T5" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="U5" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="V5" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -818,19 +781,19 @@
         <v>2005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>5</v>
@@ -839,22 +802,22 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" s="1" t="n">
         <v>0</v>
@@ -863,7 +826,7 @@
         <v>0</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="1" t="n">
         <v>0</v>
@@ -871,19 +834,13 @@
       <c r="S6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T6" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="U6" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="V6" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="X6" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y6" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -892,72 +849,66 @@
         <v>2006</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="G7" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="J7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L7" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="N7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="O7" s="1" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="1" t="n">
+      <c r="V7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -966,19 +917,19 @@
         <v>2007</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>12</v>
@@ -987,31 +938,31 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J8" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.8</v>
+        <v>0.15</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P8" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="1" t="n">
         <v>0</v>
@@ -1019,19 +970,13 @@
       <c r="S8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T8" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="U8" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="V8" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1040,72 +985,66 @@
         <v>2008</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="G9" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1" t="n">
+      <c r="L9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" s="1" t="n">
         <v>2.5</v>
       </c>
-      <c r="L9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="1" t="n">
-        <v>1</v>
+      <c r="V9" s="1" t="n">
+        <v>0.3</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X9" s="1" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Y9" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1114,19 +1053,19 @@
         <v>2009</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>0</v>
@@ -1159,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="1" t="n">
         <v>0</v>
@@ -1167,19 +1106,13 @@
       <c r="S10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T10" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="V10" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1188,19 +1121,19 @@
         <v>2010</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>6</v>
@@ -1209,22 +1142,22 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="J11" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>1.8</v>
+        <v>0.25</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="1" t="n">
         <v>0</v>
@@ -1233,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="1" t="n">
         <v>0</v>
@@ -1241,19 +1174,13 @@
       <c r="S11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T11" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="V11" s="1" t="n">
+        <v>0.8</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="X11" s="1" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Y11" s="1" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eoe/Assets/Excels/SkillConfig.xlsx
+++ b/eoe/Assets/Excels/SkillConfig.xlsx
@@ -209,13 +209,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -429,7 +433,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="20.63"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16381" min="26" style="1" width="15.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16383" min="16382" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16383" min="16382" style="2" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
@@ -524,10 +528,10 @@
         <v>26</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>1</v>

--- a/eoe/Assets/Excels/SkillConfig.xlsx
+++ b/eoe/Assets/Excels/SkillConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t xml:space="preserve">skillId</t>
   </si>
@@ -34,18 +34,15 @@
     <t xml:space="preserve">findTarget</t>
   </si>
   <si>
-    <t xml:space="preserve">trajectory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pivotStationary</t>
-  </si>
-  <si>
     <t xml:space="preserve">projectileSpeed</t>
   </si>
   <si>
     <t xml:space="preserve">projectileDuration</t>
   </si>
   <si>
+    <t xml:space="preserve">spawnAtTarget</t>
+  </si>
+  <si>
     <t xml:space="preserve">sizeMultiplier</t>
   </si>
   <si>
@@ -97,40 +94,34 @@
     <t xml:space="preserve">Nearest</t>
   </si>
   <si>
-    <t xml:space="preserve">Line</t>
+    <t xml:space="preserve">skill.shotgun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill.rifle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill.sniper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farthest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill.magic_bolt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill.aoe_blast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill.chain_lightning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill.poison_cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill.heal</t>
   </si>
   <si>
     <t xml:space="preserve">None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill.shotgun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill.rifle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill.sniper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Farthest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill.magic_bolt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill.aoe_blast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stationary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill.chain_lightning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill.poison_cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill.heal</t>
   </si>
   <si>
     <t xml:space="preserve">skill.fireball</t>
@@ -140,8 +131,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -209,7 +201,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -220,6 +212,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -414,27 +410,27 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr defaultColWidth="15.6328125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="15.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.36"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="4" style="1" width="15.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="17.54"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15.45"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="15.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="20.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="21.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="20.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="22.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="19" style="1" width="20.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="20.63"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16381" min="26" style="1" width="15.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16383" min="16382" style="2" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.54"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.45"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="20.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="21.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="20.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="22.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="18" style="1" width="20.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="20.63"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16380" min="25" style="1" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16382" min="16381" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="0" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -504,75 +500,69 @@
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>2001</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="1" t="n">
+      <c r="E2" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="F2" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="H2" s="1" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>0.1</v>
+        <v>30</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="P2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="1" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T2" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="U2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -581,66 +571,63 @@
         <v>2002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3" s="1" t="n">
         <v>7</v>
       </c>
+      <c r="F3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="H3" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="U3" s="1" t="n">
         <v>0</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -649,37 +636,37 @@
         <v>2003</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="F4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="H4" s="1" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>0</v>
@@ -691,24 +678,21 @@
         <v>0</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="1" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="U4" s="1" t="n">
         <v>0</v>
       </c>
       <c r="V4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -717,37 +701,37 @@
         <v>2004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>15</v>
       </c>
+      <c r="F5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="H5" s="1" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>0</v>
@@ -759,24 +743,21 @@
         <v>0</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="1" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="U5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -785,37 +766,37 @@
         <v>2005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="F6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="H6" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>0</v>
@@ -827,24 +808,21 @@
         <v>0</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="1" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="U6" s="1" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W6" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -853,66 +831,63 @@
         <v>2006</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="3" t="b">
+        <v>1</v>
       </c>
       <c r="H7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="I7" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" s="1" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="L7" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="M7" s="1" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="U7" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -921,40 +896,40 @@
         <v>2007</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E8" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="F8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="H8" s="1" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.15</v>
+        <v>3</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N8" s="1" t="n">
         <v>0</v>
@@ -963,24 +938,21 @@
         <v>0</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="1" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="U8" s="1" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -989,66 +961,63 @@
         <v>2008</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="b">
+        <v>1</v>
       </c>
       <c r="H9" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="1" t="n">
+      <c r="K9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="1" t="n">
         <v>2.5</v>
       </c>
-      <c r="J9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="M9" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="U9" s="1" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="W9" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1057,22 +1026,22 @@
         <v>2009</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>0</v>
+      <c r="E10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="b">
+        <v>1</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>0</v>
@@ -1099,24 +1068,21 @@
         <v>0</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="1" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="U10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1125,37 +1091,37 @@
         <v>2010</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E11" s="1" t="n">
         <v>6</v>
       </c>
+      <c r="F11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="H11" s="1" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="1" t="n">
         <v>0</v>
@@ -1167,24 +1133,21 @@
         <v>0</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="1" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W11" s="1" t="n">
         <v>0</v>
       </c>
     </row>
